--- a/test-data/TestDataCRM.xlsx
+++ b/test-data/TestDataCRM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\indhu\Desktop\Indhuja Personal\QANinjas\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF324BD2-35C2-4D2C-855F-AC8DB6B904F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186A7FC8-3C3F-4193-A899-3DCDF8FB7C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{6D1DF0C3-F339-45E7-B29D-0B0348DABBE5}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="69">
   <si>
     <t>username</t>
   </si>
@@ -84,13 +84,163 @@
     <t>USA</t>
   </si>
   <si>
-    <t>Testing purpose Accpunt Creation</t>
-  </si>
-  <si>
     <t>billingstreet</t>
   </si>
   <si>
     <t>billingpostalcode</t>
+  </si>
+  <si>
+    <t>Testing purpose Account Creation</t>
+  </si>
+  <si>
+    <t>meetingsubject</t>
+  </si>
+  <si>
+    <t>meetingstartdate</t>
+  </si>
+  <si>
+    <t>meetingstarthr</t>
+  </si>
+  <si>
+    <t>meetingstartmin</t>
+  </si>
+  <si>
+    <t>meetingenddate</t>
+  </si>
+  <si>
+    <t>meetingendhr</t>
+  </si>
+  <si>
+    <t>meetingendmin</t>
+  </si>
+  <si>
+    <t>meetingdesc</t>
+  </si>
+  <si>
+    <t>meetingcontactfname</t>
+  </si>
+  <si>
+    <t>meetingcontactemail</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-12-31</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Automation Roadmap</t>
+  </si>
+  <si>
+    <t>Updates on E2E flow</t>
+  </si>
+  <si>
+    <t>Indu</t>
+  </si>
+  <si>
+    <t>Arav</t>
+  </si>
+  <si>
+    <t>indu@gmail.com</t>
+  </si>
+  <si>
+    <t>meetingcontactlname</t>
+  </si>
+  <si>
+    <t>callsubject</t>
+  </si>
+  <si>
+    <t>callstartdate</t>
+  </si>
+  <si>
+    <t>callstarthr</t>
+  </si>
+  <si>
+    <t>callstartmin</t>
+  </si>
+  <si>
+    <t>callduration</t>
+  </si>
+  <si>
+    <t>Automation discussion</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>happy</t>
+  </si>
+  <si>
+    <t>nova</t>
+  </si>
+  <si>
+    <t>happy@nova.com</t>
+  </si>
+  <si>
+    <t>calldesc</t>
+  </si>
+  <si>
+    <t>Testing Calendar - Schedule calls functionality</t>
+  </si>
+  <si>
+    <t>callinviteesfname</t>
+  </si>
+  <si>
+    <t>callinviteeslname</t>
+  </si>
+  <si>
+    <t>callinviteesemail</t>
+  </si>
+  <si>
+    <t>tasksubject</t>
+  </si>
+  <si>
+    <t>taskstartdate</t>
+  </si>
+  <si>
+    <t>taskduedate</t>
+  </si>
+  <si>
+    <t>taskpriority</t>
+  </si>
+  <si>
+    <t>taskdesc</t>
+  </si>
+  <si>
+    <t>taskstatus</t>
+  </si>
+  <si>
+    <t>taskaccount</t>
+  </si>
+  <si>
+    <t>Happy task</t>
+  </si>
+  <si>
+    <t>2026-07-16 00:00</t>
+  </si>
+  <si>
+    <t>2026-08-31 11:59</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>abcdefgh</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>Opportunity</t>
   </si>
 </sst>
 </file>
@@ -135,10 +285,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -454,18 +606,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11118C9F-B298-4F26-9F61-AF413F775E9C}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="11.9296875" customWidth="1"/>
-    <col min="4" max="4" width="21.1328125" customWidth="1"/>
-    <col min="6" max="6" width="10.19921875" style="2" customWidth="1"/>
-    <col min="7" max="8" width="10.19921875" customWidth="1"/>
-    <col min="9" max="9" width="12.1328125" customWidth="1"/>
-    <col min="10" max="10" width="10.19921875" customWidth="1"/>
+    <col min="1" max="5" width="13.1328125" customWidth="1"/>
+    <col min="6" max="6" width="13.1328125" style="2" customWidth="1"/>
+    <col min="7" max="22" width="13.1328125" customWidth="1"/>
+    <col min="23" max="23" width="11.6640625" customWidth="1"/>
+    <col min="24" max="24" width="9.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -479,10 +630,10 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
@@ -496,8 +647,89 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U1" t="s">
+        <v>28</v>
+      </c>
+      <c r="V1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -526,13 +758,102 @@
         <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="2">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="X2">
+        <v>3</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL2" s="2"/>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.45">
+      <c r="C9" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{F379BABE-671B-4DB6-879B-6434088C02C9}"/>
+    <hyperlink ref="AD2" r:id="rId2" xr:uid="{166ECEC9-0772-41DF-8349-42A28640E0E5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="F2 N2 Q2 Y2:Z2" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>